--- a/data/Test_edge1.xlsx
+++ b/data/Test_edge1.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2592</t>
+          <t>0.2604</t>
         </is>
       </c>
     </row>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,1413 +548,1277 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.01195793613442967</v>
+        <v>0.0132175967201877</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9875396774215829</v>
+        <v>0.9839220138178527</v>
       </c>
       <c r="C3" t="n">
-        <v>0.987014151128078</v>
+        <v>0.9839292246103277</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9867469657793941</v>
+        <v>0.9838050384413018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9871142517072672</v>
+        <v>0.9838997039746966</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.02391587226885934</v>
+        <v>0.02643519344037539</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9610405249456712</v>
+        <v>0.954110606675372</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9600273707553478</v>
+        <v>0.9539032497006601</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9588336229194599</v>
+        <v>0.9527056619606072</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9601706987515655</v>
+        <v>0.9538492871151197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.03587380840328901</v>
+        <v>0.03965279016056309</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9324573969700696</v>
+        <v>0.9272587337384951</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9310588758016157</v>
+        <v>0.925748882957251</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9285116106790546</v>
+        <v>0.9230754669497944</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9312015564669054</v>
+        <v>0.925864446979244</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.04783174453771868</v>
+        <v>0.05287038688075078</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9130712930822151</v>
+        <v>0.9037477820639237</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9099029739885216</v>
+        <v>0.9005557003102055</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9052989513698109</v>
+        <v>0.8955656612225129</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9103553665368802</v>
+        <v>0.9008629683590172</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.05978968067214835</v>
+        <v>0.06608798360093848</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8931347888516629</v>
+        <v>0.8800223538152601</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8876346090059786</v>
+        <v>0.87491980354517</v>
       </c>
       <c r="D7" t="n">
-        <v>0.880894126281288</v>
+        <v>0.8681334993888791</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8884834809289437</v>
+        <v>0.8755192425985272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.07174761680657801</v>
+        <v>0.07930558032112618</v>
       </c>
       <c r="B8" t="n">
-        <v>0.8680956381035272</v>
+        <v>0.8588131845654684</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8622315877768858</v>
+        <v>0.8522693571037863</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8544662730240801</v>
+        <v>0.8453630093942122</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8631134292868604</v>
+        <v>0.8531593062156146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.08370555294100769</v>
+        <v>0.09252317704131387</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8514300951603474</v>
+        <v>0.8362072805214892</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8449854947938787</v>
+        <v>0.8300539841898202</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8369179836246368</v>
+        <v>0.8228258589894984</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8460852478613771</v>
+        <v>0.830857068802773</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.09566348907543736</v>
+        <v>0.1057407737615016</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8290327482096872</v>
+        <v>0.8085503803200395</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8218994469675247</v>
+        <v>0.8045765638859882</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8139858357391682</v>
+        <v>0.7980854822107704</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8231476078588756</v>
+        <v>0.8049876819867189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.107621425209867</v>
+        <v>0.1189583704816893</v>
       </c>
       <c r="B11" t="n">
-        <v>0.803611807287231</v>
+        <v>0.7899298934794433</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8004360042497516</v>
+        <v>0.7889755134671571</v>
       </c>
       <c r="D11" t="n">
-        <v>0.793430822323139</v>
+        <v>0.7843313227894765</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8008996450004081</v>
+        <v>0.7888878942939977</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1195793613442967</v>
+        <v>0.132175967201877</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7898655285714874</v>
+        <v>0.7696619718788745</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7891962932543315</v>
+        <v>0.7699715879199373</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7842045817014422</v>
+        <v>0.7677588007935232</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7894824998561387</v>
+        <v>0.7698015949473082</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1315372974787264</v>
+        <v>0.1453935639220647</v>
       </c>
       <c r="B13" t="n">
-        <v>0.772931373506805</v>
+        <v>0.7488029981503876</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7722888808407181</v>
+        <v>0.7484629967704474</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7696214287715438</v>
+        <v>0.748649300954434</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7727770336582508</v>
+        <v>0.7485773835084879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.143495233613156</v>
+        <v>0.1586111606422524</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7480985731109241</v>
+        <v>0.7331297021927066</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7500081438109635</v>
+        <v>0.7306747644416861</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7491921976758525</v>
+        <v>0.732766095465754</v>
       </c>
       <c r="E14" t="n">
-        <v>0.750199244154141</v>
+        <v>0.7313614889552089</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.1554531697475857</v>
+        <v>0.17182875736244</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7338813226289934</v>
+        <v>0.7106286410357321</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7334850782936921</v>
+        <v>0.7060941400568147</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7341247565866652</v>
+        <v>0.709831532478686</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7345656082891638</v>
+        <v>0.7073886816055712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.1674111058820154</v>
+        <v>0.1850463540826277</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7176184290991224</v>
+        <v>0.6745717863504215</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7151422297176616</v>
+        <v>0.6686619196072496</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7179037739042273</v>
+        <v>0.6723033321303132</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7167047262120916</v>
+        <v>0.670201999605055</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.179369042016445</v>
+        <v>0.1982639508028154</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6842347133792083</v>
+        <v>0.646951551803991</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6842469953950833</v>
+        <v>0.6401382466561782</v>
       </c>
       <c r="D17" t="n">
-        <v>0.687825004786609</v>
+        <v>0.6431554804484144</v>
       </c>
       <c r="E17" t="n">
-        <v>0.685293442145004</v>
+        <v>0.6417234073698236</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.1913269781508747</v>
+        <v>0.2114815475230031</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6524313114202781</v>
+        <v>0.6240596374750715</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6482303237979647</v>
+        <v>0.6186089223616417</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6507615568534754</v>
+        <v>0.6211932477989626</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6502507924857392</v>
+        <v>0.6198296030000577</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.2032849142853044</v>
+        <v>0.2246991442431908</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6349067012619758</v>
+        <v>0.5843300068312861</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6291977153153371</v>
+        <v>0.5796672384044533</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6312191241290335</v>
+        <v>0.580848140004139</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6314924358632602</v>
+        <v>0.580618094134196</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.215242850419734</v>
+        <v>0.2379167409633785</v>
       </c>
       <c r="B20" t="n">
-        <v>0.6084752397937518</v>
+        <v>0.5542492264722616</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6077653296811145</v>
+        <v>0.5503186781969759</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6084267953332551</v>
+        <v>0.5492073143709131</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6089451374411713</v>
+        <v>0.5509364463060815</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.2272007865541637</v>
+        <v>0.2511343376835662</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5720277248360522</v>
+        <v>0.5298860700861325</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5673003481447383</v>
+        <v>0.5245741827135603</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5661614448486099</v>
+        <v>0.5210756712880695</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5691661299223355</v>
+        <v>0.5253438766066829</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.2391587226885934</v>
+        <v>0.2643519344037539</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5440086845260151</v>
+        <v>0.4978252213823779</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5390518455249854</v>
+        <v>0.487540298259948</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5356671108024782</v>
+        <v>0.4827211019648786</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5408689303801549</v>
+        <v>0.4893307292496641</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.251116658823023</v>
+        <v>0.2775695311239416</v>
       </c>
       <c r="B23" t="n">
-        <v>0.5202106753072454</v>
+        <v>0.4656064120347865</v>
       </c>
       <c r="C23" t="n">
-        <v>0.5182581264649708</v>
+        <v>0.4533167608405608</v>
       </c>
       <c r="D23" t="n">
-        <v>0.512458116332712</v>
+        <v>0.4462525530016028</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5197186123372232</v>
+        <v>0.4553792413259423</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.2630745949574527</v>
+        <v>0.2907871278441293</v>
       </c>
       <c r="B24" t="n">
-        <v>0.4981825407733657</v>
+        <v>0.4489264469416818</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4871130089782792</v>
+        <v>0.4379272335515321</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4806832101346447</v>
+        <v>0.4295748571110402</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4903685734829862</v>
+        <v>0.439651876089398</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.2750325310918824</v>
+        <v>0.304004724564317</v>
       </c>
       <c r="B25" t="n">
-        <v>0.4618281938866344</v>
+        <v>0.4263141153640989</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4483982078930895</v>
+        <v>0.4175599950351877</v>
       </c>
       <c r="D25" t="n">
-        <v>0.439434190595428</v>
+        <v>0.4094362815243655</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4518568732081714</v>
+        <v>0.4188664075296002</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.2869904672263121</v>
+        <v>0.3172223212845047</v>
       </c>
       <c r="B26" t="n">
-        <v>0.4449714700422195</v>
+        <v>0.3850500264088302</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4348667313377398</v>
+        <v>0.3794364408259939</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4235286983064329</v>
+        <v>0.3718954475583909</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4378836478294344</v>
+        <v>0.3801029995569239</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.2989484033607417</v>
+        <v>0.3304399180046924</v>
       </c>
       <c r="B27" t="n">
-        <v>0.4382995840211567</v>
+        <v>0.3504347389195153</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4268814991821178</v>
+        <v>0.3470440644804934</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4169618451286988</v>
+        <v>0.340865263134544</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4298937592345157</v>
+        <v>0.3473429311333288</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.3109063394951714</v>
+        <v>0.3436575147248801</v>
       </c>
       <c r="B28" t="n">
-        <v>0.3950694630678778</v>
+        <v>0.3136976059505218</v>
       </c>
       <c r="C28" t="n">
-        <v>0.387143921400557</v>
+        <v>0.3120113536319009</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3779722607842</v>
+        <v>0.3063697659452714</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3892420235322288</v>
+        <v>0.3120241120834555</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.3228642756296011</v>
+        <v>0.3568751114450678</v>
       </c>
       <c r="B29" t="n">
-        <v>0.3607881406925453</v>
+        <v>0.2678795460380772</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3567221127146094</v>
+        <v>0.267275325953553</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3478622219840343</v>
+        <v>0.2617987490943812</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3582420227785916</v>
+        <v>0.2670215099465348</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.3348222117640308</v>
+        <v>0.3700927081652555</v>
       </c>
       <c r="B30" t="n">
-        <v>0.334604192153296</v>
+        <v>0.2229819862152089</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3300968971178796</v>
+        <v>0.2194987215655385</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3224184863033317</v>
+        <v>0.214621770578361</v>
       </c>
       <c r="E30" t="n">
-        <v>0.331515686291886</v>
+        <v>0.2199248003709365</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.3467801478984604</v>
+        <v>0.3833103048854432</v>
       </c>
       <c r="B31" t="n">
-        <v>0.2952948021456816</v>
+        <v>0.1879081230097136</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2931576002778364</v>
+        <v>0.1825858168408386</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2859749109425012</v>
+        <v>0.1792722264052675</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2944847079350507</v>
+        <v>0.1834625304673847</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.3587380840328901</v>
+        <v>0.3965279016056309</v>
       </c>
       <c r="B32" t="n">
-        <v>0.2508364873668336</v>
+        <v>0.1523616889766308</v>
       </c>
       <c r="C32" t="n">
-        <v>0.25076951078767</v>
+        <v>0.1446843541965355</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2435107201474466</v>
+        <v>0.1417546954672405</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2515668025462391</v>
+        <v>0.1459169547465146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.3706960201673197</v>
+        <v>0.4097454983258186</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2121485770929091</v>
+        <v>0.1178613016544126</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2081228151464835</v>
+        <v>0.1067029071009027</v>
       </c>
       <c r="D33" t="n">
-        <v>0.202997367474729</v>
+        <v>0.1034367465367537</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2089917442119301</v>
+        <v>0.1084882395646879</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.3826539563017494</v>
+        <v>0.4229630950460063</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1836514836252088</v>
+        <v>0.09280703173209083</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1797045191953346</v>
+        <v>0.0828130290801847</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1758872075765961</v>
+        <v>0.07929730037147659</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1809755400339934</v>
+        <v>0.08414992051100635</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.3946118924361791</v>
+        <v>0.436180691766194</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1504610026413736</v>
+        <v>0.07067988539402141</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1461650974129095</v>
+        <v>0.06190235765152125</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1412942894972268</v>
+        <v>0.05725066057709906</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1474360216352557</v>
+        <v>0.06297003857434197</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.4065698285706087</v>
+        <v>0.4493982884863816</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1218050279971075</v>
+        <v>0.05078307166394397</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1130139124312156</v>
+        <v>0.04227823565776783</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1094131552373614</v>
+        <v>0.03677132053700086</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1145640645627027</v>
+        <v>0.04325017178963448</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.4185277647050384</v>
+        <v>0.4626158852065694</v>
       </c>
       <c r="B37" t="n">
-        <v>0.09832823116376976</v>
+        <v>0.04045063481237223</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0884747101122844</v>
+        <v>0.03118680885724446</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08515986315990413</v>
+        <v>0.02588164291846952</v>
       </c>
       <c r="E37" t="n">
-        <v>0.0903362703596904</v>
+        <v>0.03238268362611091</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.4304857008394681</v>
+        <v>0.4758334819267571</v>
       </c>
       <c r="B38" t="n">
-        <v>0.07656563607217005</v>
+        <v>0.03461458938641043</v>
       </c>
       <c r="C38" t="n">
-        <v>0.06742431385797011</v>
+        <v>0.02399775836776863</v>
       </c>
       <c r="D38" t="n">
-        <v>0.06219390664663899</v>
+        <v>0.01781434461613671</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06891112657610601</v>
+        <v>0.0256518799884144</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.4424436369738978</v>
+        <v>0.4890510786469447</v>
       </c>
       <c r="B39" t="n">
-        <v>0.05887507575357714</v>
+        <v>0.02714314563427269</v>
       </c>
       <c r="C39" t="n">
-        <v>0.05021430049746529</v>
+        <v>0.01667638807411832</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0442582102166</v>
+        <v>0.01011638075395234</v>
       </c>
       <c r="E39" t="n">
-        <v>0.05150248307591219</v>
+        <v>0.01833901778643445</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.4544015731083275</v>
+        <v>0.5022686753671325</v>
       </c>
       <c r="B40" t="n">
-        <v>0.04581352807054562</v>
+        <v>0.02193877272263607</v>
       </c>
       <c r="C40" t="n">
-        <v>0.03523546583120037</v>
+        <v>0.009525424222207979</v>
       </c>
       <c r="D40" t="n">
-        <v>0.03034264498088444</v>
+        <v>0.004893110470074322</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03713531990459467</v>
+        <v>0.01164828607544934</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.4663595092427571</v>
+        <v>0.5154862720873201</v>
       </c>
       <c r="B41" t="n">
-        <v>0.04121035249725186</v>
+        <v>0.01866572166445451</v>
       </c>
       <c r="C41" t="n">
-        <v>0.02885769252098053</v>
+        <v>0.004857414433325334</v>
       </c>
       <c r="D41" t="n">
-        <v>0.02392539385533462</v>
+        <v>0.00588976894574535</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03113540078337071</v>
+        <v>0.007336057156046122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.4783174453771868</v>
+        <v>0.5287038688075079</v>
       </c>
       <c r="B42" t="n">
-        <v>0.03245591139017968</v>
+        <v>0.02588516643492466</v>
       </c>
       <c r="C42" t="n">
-        <v>0.02111240747855185</v>
+        <v>0.01601377522951782</v>
       </c>
       <c r="D42" t="n">
-        <v>0.01390827719775902</v>
+        <v>0.01483203887860529</v>
       </c>
       <c r="E42" t="n">
-        <v>0.02314289375192839</v>
+        <v>0.01722043989371835</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.4902753815116164</v>
+        <v>0.5419214655276955</v>
       </c>
       <c r="B43" t="n">
-        <v>0.02440496072397526</v>
+        <v>0.0355935566863325</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0139478878926269</v>
+        <v>0.02333330284672468</v>
       </c>
       <c r="D43" t="n">
-        <v>0.008509071230271493</v>
+        <v>0.02223731641422066</v>
       </c>
       <c r="E43" t="n">
-        <v>0.01571268506698341</v>
+        <v>0.02468744388880371</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.5022333176460461</v>
+        <v>0.5551390622478832</v>
       </c>
       <c r="B44" t="n">
-        <v>0.02100046516626628</v>
+        <v>0.04260192700784943</v>
       </c>
       <c r="C44" t="n">
-        <v>0.009581789700509611</v>
+        <v>0.0308387674888963</v>
       </c>
       <c r="D44" t="n">
-        <v>0.007300790601316579</v>
+        <v>0.03368194121776284</v>
       </c>
       <c r="E44" t="n">
-        <v>0.01145294115244745</v>
+        <v>0.03203361221419811</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.5141912537804758</v>
+        <v>0.568356658968071</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0155091831380059</v>
+        <v>0.04251586631125721</v>
       </c>
       <c r="C45" t="n">
-        <v>0.001971479126427879</v>
+        <v>0.0335899958695511</v>
       </c>
       <c r="D45" t="n">
-        <v>0.004986518597127938</v>
+        <v>0.03544084036682454</v>
       </c>
       <c r="E45" t="n">
-        <v>0.004601754487719088</v>
+        <v>0.03450924216055391</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.5261491899149054</v>
+        <v>0.5815742556882586</v>
       </c>
       <c r="B46" t="n">
-        <v>0.02124246130509673</v>
+        <v>0.04843208781387466</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0142023578964837</v>
+        <v>0.03717607821130952</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01354597108269661</v>
+        <v>0.03683765673486212</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0151590704239834</v>
+        <v>0.03836168386088142</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.5381071260493351</v>
+        <v>0.5947918524084463</v>
       </c>
       <c r="B47" t="n">
-        <v>0.02932166687912731</v>
+        <v>0.05729911871396348</v>
       </c>
       <c r="C47" t="n">
-        <v>0.02070863545411833</v>
+        <v>0.04287592944316692</v>
       </c>
       <c r="D47" t="n">
-        <v>0.01758013037600364</v>
+        <v>0.04483825420199653</v>
       </c>
       <c r="E47" t="n">
-        <v>0.02161535837147176</v>
+        <v>0.04478628983277137</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.5500650621837648</v>
+        <v>0.608009449128634</v>
       </c>
       <c r="B48" t="n">
-        <v>0.03780320646247925</v>
+        <v>0.0470562602148697</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02758644791197298</v>
+        <v>0.03593782119674734</v>
       </c>
       <c r="D48" t="n">
-        <v>0.02763264116982703</v>
+        <v>0.03911761163384003</v>
       </c>
       <c r="E48" t="n">
-        <v>0.02872426861914388</v>
+        <v>0.03755204901610202</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.5620229983181945</v>
+        <v>0.6212270458488217</v>
       </c>
       <c r="B49" t="n">
-        <v>0.03988563584540929</v>
+        <v>0.03792133466140495</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03222789646325564</v>
+        <v>0.02686696164224767</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03385841814139359</v>
+        <v>0.02968719103125993</v>
       </c>
       <c r="E49" t="n">
-        <v>0.03328485511892661</v>
+        <v>0.02807901896121943</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.5739809344526241</v>
+        <v>0.6344446425690095</v>
       </c>
       <c r="B50" t="n">
-        <v>0.03959803962718787</v>
+        <v>0.05209731465928195</v>
       </c>
       <c r="C50" t="n">
-        <v>0.03188558159534933</v>
+        <v>0.03894909642619599</v>
       </c>
       <c r="D50" t="n">
-        <v>0.03199643155573199</v>
+        <v>0.04054891458703155</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03259272271549486</v>
+        <v>0.04065077713469629</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.5859388705870539</v>
+        <v>0.6476622392891971</v>
       </c>
       <c r="B51" t="n">
-        <v>0.04803484914890225</v>
+        <v>0.05977354737834716</v>
       </c>
       <c r="C51" t="n">
-        <v>0.03541438400437799</v>
+        <v>0.05310523197837014</v>
       </c>
       <c r="D51" t="n">
-        <v>0.03450034517927387</v>
+        <v>0.05522031606599152</v>
       </c>
       <c r="E51" t="n">
-        <v>0.03700969301486812</v>
+        <v>0.0538811078604699</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.5978968067214835</v>
+        <v>0.6608798360093848</v>
       </c>
       <c r="B52" t="n">
-        <v>0.05132669255921852</v>
+        <v>0.06108780644422108</v>
       </c>
       <c r="C52" t="n">
-        <v>0.03920835256419025</v>
+        <v>0.05284922722316382</v>
       </c>
       <c r="D52" t="n">
-        <v>0.04053637543982318</v>
+        <v>0.051582888809731</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04089222428469502</v>
+        <v>0.05375478578208447</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.6098547428559131</v>
+        <v>0.6740974327295725</v>
       </c>
       <c r="B53" t="n">
-        <v>0.04634812819482885</v>
+        <v>0.07267583316872753</v>
       </c>
       <c r="C53" t="n">
-        <v>0.03715395535338839</v>
+        <v>0.05849926645567044</v>
       </c>
       <c r="D53" t="n">
-        <v>0.04038315267454362</v>
+        <v>0.05477002388321442</v>
       </c>
       <c r="E53" t="n">
-        <v>0.03716624758381799</v>
+        <v>0.06073843611061383</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.6218126789903428</v>
+        <v>0.6873150294497602</v>
       </c>
       <c r="B54" t="n">
-        <v>0.03724440513783928</v>
+        <v>0.0642135163984983</v>
       </c>
       <c r="C54" t="n">
-        <v>0.02581194835329494</v>
+        <v>0.05550459233655367</v>
       </c>
       <c r="D54" t="n">
-        <v>0.02999138090591893</v>
+        <v>0.05698579744388825</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02508009162688258</v>
+        <v>0.05699863324631431</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.6337706151247725</v>
+        <v>0.7005326261699478</v>
       </c>
       <c r="B55" t="n">
-        <v>0.04003161037447119</v>
+        <v>0.05742296029667027</v>
       </c>
       <c r="C55" t="n">
-        <v>0.02834989595980514</v>
+        <v>0.05226565703185991</v>
       </c>
       <c r="D55" t="n">
-        <v>0.03061157667927642</v>
+        <v>0.05660551198091739</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0283226827391687</v>
+        <v>0.05331834573493621</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>0.6457285512592021</v>
+        <v>0.7137502228901356</v>
       </c>
       <c r="B56" t="n">
-        <v>0.05475542322897759</v>
+        <v>0.05265965812588526</v>
       </c>
       <c r="C56" t="n">
-        <v>0.04940099449880928</v>
+        <v>0.04541542452745884</v>
       </c>
       <c r="D56" t="n">
-        <v>0.05038135373629962</v>
+        <v>0.04727116413800651</v>
       </c>
       <c r="E56" t="n">
-        <v>0.04909768221250963</v>
+        <v>0.04663342443844812</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>0.6576864873936318</v>
+        <v>0.7269678196103233</v>
       </c>
       <c r="B57" t="n">
-        <v>0.05586021068577424</v>
+        <v>0.03869764436160458</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0510087301512983</v>
+        <v>0.03635025225443857</v>
       </c>
       <c r="D57" t="n">
-        <v>0.04973924255187692</v>
+        <v>0.03691714114424442</v>
       </c>
       <c r="E57" t="n">
-        <v>0.05188402413363362</v>
+        <v>0.03671538485613241</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0.6696444235280615</v>
+        <v>0.7401854163305109</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0677024822187227</v>
+        <v>0.01519521888165329</v>
       </c>
       <c r="C58" t="n">
-        <v>0.05727550321340089</v>
+        <v>0.01867788317885149</v>
       </c>
       <c r="D58" t="n">
-        <v>0.05021342503209938</v>
+        <v>0.02361031100100992</v>
       </c>
       <c r="E58" t="n">
-        <v>0.06012621797742473</v>
+        <v>0.0183298090593969</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.6816023596624912</v>
+        <v>0.7534030130506987</v>
       </c>
       <c r="B59" t="n">
-        <v>0.07084504034753492</v>
+        <v>0.01496755687367168</v>
       </c>
       <c r="C59" t="n">
-        <v>0.05951554148394578</v>
+        <v>0.01844829902299587</v>
       </c>
       <c r="D59" t="n">
-        <v>0.05583491562484039</v>
+        <v>0.0215490970852305</v>
       </c>
       <c r="E59" t="n">
-        <v>0.06122836496913693</v>
+        <v>0.01719807051046898</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.6935602957969208</v>
+        <v>0.7666206097708863</v>
       </c>
       <c r="B60" t="n">
-        <v>0.04889928911604125</v>
+        <v>0.01665237160741291</v>
       </c>
       <c r="C60" t="n">
-        <v>0.04657473165319603</v>
+        <v>0.02604943982300327</v>
       </c>
       <c r="D60" t="n">
-        <v>0.05015611420393377</v>
+        <v>0.02883153777376748</v>
       </c>
       <c r="E60" t="n">
-        <v>0.04706606297447433</v>
+        <v>0.02420605639676003</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.7055182319313504</v>
+        <v>0.779838206491074</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0510394593460607</v>
+        <v>0.02774420892640965</v>
       </c>
       <c r="C61" t="n">
-        <v>0.04536557695536132</v>
+        <v>0.03059335789924102</v>
       </c>
       <c r="D61" t="n">
-        <v>0.04828630442862716</v>
+        <v>0.03401000166608944</v>
       </c>
       <c r="E61" t="n">
-        <v>0.04643387188055921</v>
+        <v>0.03035423038833409</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.7174761680657802</v>
+        <v>0.7930558032112618</v>
       </c>
       <c r="B62" t="n">
-        <v>0.04764932961268137</v>
+        <v>0.01875662070090316</v>
       </c>
       <c r="C62" t="n">
-        <v>0.04040239403701771</v>
+        <v>0.02148115486607113</v>
       </c>
       <c r="D62" t="n">
-        <v>0.04071687008198519</v>
+        <v>0.02261519714015016</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0412709411770944</v>
+        <v>0.02104729832044057</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>0.7294341042002098</v>
+        <v>0.8062733999314494</v>
       </c>
       <c r="B63" t="n">
-        <v>0.03151756230141976</v>
+        <v>0.01873509211131502</v>
       </c>
       <c r="C63" t="n">
-        <v>0.03218509041792861</v>
+        <v>0.02030215305042855</v>
       </c>
       <c r="D63" t="n">
-        <v>0.03342674691239433</v>
+        <v>0.02131094583815554</v>
       </c>
       <c r="E63" t="n">
-        <v>0.03375458600870992</v>
+        <v>0.02006949907333531</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0.7413920403346395</v>
+        <v>0.8194909966516372</v>
       </c>
       <c r="B64" t="n">
-        <v>0.02493461427764001</v>
+        <v>0.01994138712892436</v>
       </c>
       <c r="C64" t="n">
-        <v>0.02177844404503421</v>
+        <v>0.01544162914679005</v>
       </c>
       <c r="D64" t="n">
-        <v>0.02474336320890837</v>
+        <v>0.01660356197194703</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02307972453768575</v>
+        <v>0.01640312026478933</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0.7533499764690692</v>
+        <v>0.8327085933718248</v>
       </c>
       <c r="B65" t="n">
-        <v>0.01837251620283202</v>
+        <v>0.02858422769020144</v>
       </c>
       <c r="C65" t="n">
-        <v>0.02459020948911151</v>
+        <v>0.02301942822110941</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0287803723276601</v>
+        <v>0.02400768216961851</v>
       </c>
       <c r="E65" t="n">
-        <v>0.0241633501189598</v>
+        <v>0.02421084111070793</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>0.7653079126034988</v>
+        <v>0.8459261900920125</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0161444961782403</v>
+        <v>0.009656550195285244</v>
       </c>
       <c r="C66" t="n">
-        <v>0.02918347690996034</v>
+        <v>0.00749744816674868</v>
       </c>
       <c r="D66" t="n">
-        <v>0.03372377546107882</v>
+        <v>0.01074895044661642</v>
       </c>
       <c r="E66" t="n">
-        <v>0.02806731748982019</v>
+        <v>0.007545593189758317</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.7772658487379285</v>
+        <v>0.8591437868122003</v>
       </c>
       <c r="B67" t="n">
-        <v>0.02224158923233645</v>
+        <v>0.0150296666071461</v>
       </c>
       <c r="C67" t="n">
-        <v>0.03279159103032187</v>
+        <v>0.008379758326094435</v>
       </c>
       <c r="D67" t="n">
-        <v>0.03627333326623414</v>
+        <v>0.007836515430714041</v>
       </c>
       <c r="E67" t="n">
-        <v>0.02847098496062714</v>
+        <v>0.009456906681845088</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.7892237848723582</v>
+        <v>0.8723613835323879</v>
       </c>
       <c r="B68" t="n">
-        <v>0.01934878184462045</v>
+        <v>0.01426887386053433</v>
       </c>
       <c r="C68" t="n">
-        <v>0.02295105594785422</v>
+        <v>0.004320824820883249</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0238411121150884</v>
+        <v>0.006470637083485556</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01956110830244622</v>
+        <v>0.005350935494692782</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.8011817210067879</v>
+        <v>0.8855789802525756</v>
       </c>
       <c r="B69" t="n">
-        <v>0.01875046782539486</v>
+        <v>0.01381932615658554</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0187874540227537</v>
+        <v>0.001246128887791464</v>
       </c>
       <c r="D69" t="n">
-        <v>0.01627031027076682</v>
+        <v>0.007490907593348801</v>
       </c>
       <c r="E69" t="n">
-        <v>0.01995525949868452</v>
+        <v>0.002514669621869485</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.8131396571412175</v>
+        <v>0.8987965769727633</v>
       </c>
       <c r="B70" t="n">
-        <v>0.02443066989707645</v>
+        <v>0.03875733903134016</v>
       </c>
       <c r="C70" t="n">
-        <v>0.01572435112239291</v>
+        <v>0.02073383379418433</v>
       </c>
       <c r="D70" t="n">
-        <v>0.01620490546248969</v>
+        <v>0.01255020719825829</v>
       </c>
       <c r="E70" t="n">
-        <v>0.01681994642619841</v>
+        <v>0.02320780296275162</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.8250975932756471</v>
+        <v>0.912014173692951</v>
       </c>
       <c r="B71" t="n">
-        <v>0.02977399118765648</v>
+        <v>0.02346823157226591</v>
       </c>
       <c r="C71" t="n">
-        <v>0.02702566068188421</v>
+        <v>0.01809371159437296</v>
       </c>
       <c r="D71" t="n">
-        <v>0.02769950027859296</v>
+        <v>0.01343867120971689</v>
       </c>
       <c r="E71" t="n">
-        <v>0.02663261217442454</v>
+        <v>0.0164355661067487</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.8370555294100769</v>
+        <v>0.9252317704131388</v>
       </c>
       <c r="B72" t="n">
-        <v>0.03085492015318466</v>
+        <v>0.01217448607396179</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0256739995964138</v>
+        <v>0.01646228718520373</v>
       </c>
       <c r="D72" t="n">
-        <v>0.02532178718242203</v>
+        <v>0.02236312122142628</v>
       </c>
       <c r="E72" t="n">
-        <v>0.02745857342161707</v>
+        <v>0.01512757703302036</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.8490134655445065</v>
+        <v>0.9384493671333264</v>
       </c>
       <c r="B73" t="n">
-        <v>0.01689485545810986</v>
+        <v>0.01054724846052516</v>
       </c>
       <c r="C73" t="n">
-        <v>0.007085714732946216</v>
+        <v>0.009600406314195146</v>
       </c>
       <c r="D73" t="n">
-        <v>0.007569305036328963</v>
+        <v>0.01353140319323098</v>
       </c>
       <c r="E73" t="n">
-        <v>0.006893702813464604</v>
+        <v>0.009826730538717656</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0.8609714016789362</v>
+        <v>0.9516669638535141</v>
       </c>
       <c r="B74" t="n">
-        <v>0.01486912658639855</v>
+        <v>0.01446965376164696</v>
       </c>
       <c r="C74" t="n">
-        <v>0.009012162662934951</v>
+        <v>0.01145246778780106</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0100136425905577</v>
+        <v>0.009539540353324339</v>
       </c>
       <c r="E74" t="n">
-        <v>0.007407489771454424</v>
+        <v>0.01224855438091345</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.8729293378133659</v>
+        <v>0.9648845605737018</v>
       </c>
       <c r="B75" t="n">
-        <v>0.01260355330413282</v>
+        <v>0.007547440364027169</v>
       </c>
       <c r="C75" t="n">
-        <v>0.01566459510782597</v>
+        <v>0.009028842706028928</v>
       </c>
       <c r="D75" t="n">
-        <v>0.01529396973630503</v>
+        <v>0.01059755486064713</v>
       </c>
       <c r="E75" t="n">
-        <v>0.01111769606029245</v>
+        <v>0.008622602874999332</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.8848872739477955</v>
+        <v>0.9781021572938895</v>
       </c>
       <c r="B76" t="n">
-        <v>0.01725470667266811</v>
+        <v>0.01021118946374349</v>
       </c>
       <c r="C76" t="n">
-        <v>0.01195381029789906</v>
+        <v>0.01442972883177352</v>
       </c>
       <c r="D76" t="n">
-        <v>0.01058532218242873</v>
+        <v>0.01545789404746493</v>
       </c>
       <c r="E76" t="n">
-        <v>0.009357797820087907</v>
+        <v>0.01401227621954377</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.8968452100822252</v>
+        <v>0.9913197540140772</v>
       </c>
       <c r="B77" t="n">
-        <v>0.041942748741716</v>
+        <v>0.007369548333677698</v>
       </c>
       <c r="C77" t="n">
-        <v>0.02141677875690739</v>
+        <v>0.003248006355640915</v>
       </c>
       <c r="D77" t="n">
-        <v>0.01876046038870478</v>
+        <v>0.003353958799374052</v>
       </c>
       <c r="E77" t="n">
-        <v>0.02178849447105567</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>0.9088031462166549</v>
-      </c>
-      <c r="B78" t="n">
-        <v>0.02199312518337086</v>
-      </c>
-      <c r="C78" t="n">
-        <v>0.02813599282874449</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.02073542391779905</v>
-      </c>
-      <c r="E78" t="n">
-        <v>0.02446352179711667</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>0.9207610823510846</v>
-      </c>
-      <c r="B79" t="n">
-        <v>0.007205454177238673</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.01606193084156451</v>
-      </c>
-      <c r="D79" t="n">
-        <v>0.01693254409999821</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0.01602756690150318</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>0.9327190184855142</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0.006780863666701566</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.004238567225023653</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.01073929009708634</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0.007987556171975649</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>0.9446769546199438</v>
-      </c>
-      <c r="B81" t="n">
-        <v>0.01501487604007987</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.01337647992776557</v>
-      </c>
-      <c r="D81" t="n">
-        <v>0.009528890704241301</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0.007603343201747885</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>0.9566348907543736</v>
-      </c>
-      <c r="B82" t="n">
-        <v>0.003445788006222329</v>
-      </c>
-      <c r="C82" t="n">
-        <v>0.007486723736929095</v>
-      </c>
-      <c r="D82" t="n">
-        <v>0.004250696543590821</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0.005341573861526232</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>0.9685928268888032</v>
-      </c>
-      <c r="B83" t="n">
-        <v>0.01991844670214648</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.02549300448784246</v>
-      </c>
-      <c r="D83" t="n">
-        <v>0.02970004239365246</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0.02536861509117532</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>0.9805507630232329</v>
-      </c>
-      <c r="B84" t="n">
-        <v>0.01966687868613172</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.02152262384335177</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.02188713726014</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.02558258152684506</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>0.9925086991576626</v>
-      </c>
-      <c r="B85" t="n">
-        <v>0.01065981704661724</v>
-      </c>
-      <c r="C85" t="n">
-        <v>0.01036909371106596</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0.01200710727752815</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0.007285094252728769</v>
+        <v>0.001803070699980756</v>
       </c>
     </row>
   </sheetData>
@@ -1991,7 +1855,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
     </row>
@@ -2003,7 +1867,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
     </row>
@@ -2015,7 +1879,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
     </row>
@@ -2027,7 +1891,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.9</t>
         </is>
       </c>
     </row>
